--- a/data/trans_camb/P6902-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P6902-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 30,85</t>
+          <t>3,35; 30,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 39,83</t>
+          <t>6,04; 39,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,87; 39,09</t>
+          <t>7,6; 40,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 36,29</t>
+          <t>-14,5; 34,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 28,26</t>
+          <t>-20,66; 28,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 37,65</t>
+          <t>-1,32; 39,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 27,71</t>
+          <t>3,52; 28,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 31,34</t>
+          <t>2,91; 31,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,36; 36,83</t>
+          <t>12,46; 37,04</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,37; 252,96</t>
+          <t>10,97; 249,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,48; 307,89</t>
+          <t>20,88; 297,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,85; 299,63</t>
+          <t>27,93; 312,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,34; 125,44</t>
+          <t>-27,25; 122,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,65; 96,53</t>
+          <t>-41,06; 102,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 138,95</t>
+          <t>-2,37; 151,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,52; 133,58</t>
+          <t>11,28; 153,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 157,87</t>
+          <t>9,26; 159,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,69; 201,48</t>
+          <t>38,33; 187,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 20,64</t>
+          <t>-6,9; 20,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 13,36</t>
+          <t>-13,82; 13,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 23,9</t>
+          <t>-2,34; 23,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 29,84</t>
+          <t>-7,46; 29,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 26,41</t>
+          <t>-11,73; 25,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 32,7</t>
+          <t>1,48; 33,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 19,86</t>
+          <t>-1,93; 19,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 12,86</t>
+          <t>-8,77; 13,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,37; 23,89</t>
+          <t>5,5; 24,84</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 57,3</t>
+          <t>-13,67; 58,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,48; 36,85</t>
+          <t>-27,57; 33,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 61,7</t>
+          <t>-4,98; 64,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 87,4</t>
+          <t>-13,06; 82,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 75,77</t>
+          <t>-22,73; 73,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 101,05</t>
+          <t>3,8; 103,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 51,82</t>
+          <t>-4,32; 48,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 32,52</t>
+          <t>-18,6; 33,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 61,6</t>
+          <t>10,15; 64,69</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 23,62</t>
+          <t>-5,56; 25,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,23; 4,66</t>
+          <t>-23,24; 3,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 37,94</t>
+          <t>5,99; 40,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 10,82</t>
+          <t>-30,37; 9,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 21,0</t>
+          <t>-18,86; 17,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,07; 12,02</t>
+          <t>-56,97; 11,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 15,35</t>
+          <t>-8,29; 16,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 5,73</t>
+          <t>-17,14; 6,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-25,13; 24,16</t>
+          <t>-24,2; 23,29</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 64,55</t>
+          <t>-13,26; 71,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,84; 14,23</t>
+          <t>-46,94; 9,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,37; 109,05</t>
+          <t>12,52; 114,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 17,65</t>
+          <t>-40,85; 15,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 39,27</t>
+          <t>-24,89; 33,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,6; 19,53</t>
+          <t>-72,29; 19,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 36,91</t>
+          <t>-15,79; 37,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,9; 14,11</t>
+          <t>-30,69; 14,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-45,45; 51,15</t>
+          <t>-45,3; 49,53</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 4,85</t>
+          <t>-23,39; 4,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 14,81</t>
+          <t>-13,25; 13,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,27; 33,95</t>
+          <t>9,74; 33,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 25,59</t>
+          <t>-6,56; 27,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 32,67</t>
+          <t>-0,02; 33,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 32,39</t>
+          <t>3,37; 32,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 10,18</t>
+          <t>-11,06; 10,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 16,63</t>
+          <t>-2,61; 17,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,88; 28,32</t>
+          <t>10,39; 29,12</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,94; 9,63</t>
+          <t>-38,47; 9,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 27,24</t>
+          <t>-21,6; 24,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,69; 66,73</t>
+          <t>15,35; 66,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 60,29</t>
+          <t>-11,03; 63,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,67; 74,18</t>
+          <t>0,23; 79,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,12; 77,8</t>
+          <t>6,41; 76,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 19,51</t>
+          <t>-18,49; 21,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 33,14</t>
+          <t>-4,6; 35,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,27; 56,55</t>
+          <t>17,55; 57,75</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 10,75</t>
+          <t>-3,74; 10,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 6,81</t>
+          <t>-7,96; 6,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,83; 25,95</t>
+          <t>11,14; 25,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 15,3</t>
+          <t>-3,92; 16,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 18,09</t>
+          <t>-0,21; 19,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 19,12</t>
+          <t>-9,75; 18,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 10,81</t>
+          <t>-0,8; 11,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 9,6</t>
+          <t>-1,51; 9,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,85; 21,39</t>
+          <t>5,18; 21,17</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 25,81</t>
+          <t>-8,34; 25,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 16,88</t>
+          <t>-17,57; 16,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25,51; 64,31</t>
+          <t>23,74; 63,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 33,11</t>
+          <t>-6,75; 34,81</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 39,78</t>
+          <t>-0,39; 41,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 40,44</t>
+          <t>-17,14; 38,56</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 25,55</t>
+          <t>-1,52; 25,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 22,4</t>
+          <t>-3,23; 22,95</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11,16; 49,41</t>
+          <t>11,51; 48,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6902-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P6902-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24,84</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,49</t>
+          <t>20,39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25,22</t>
+          <t>26,8</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 30,87</t>
+          <t>1,87; 30,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 39,28</t>
+          <t>4,06; 37,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 40,33</t>
+          <t>10,43; 42,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 34,74</t>
+          <t>-10,69; 37,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 28,9</t>
+          <t>-21,61; 27,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 39,1</t>
+          <t>-1,94; 38,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 28,57</t>
+          <t>5,24; 29,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 31,09</t>
+          <t>3,02; 30,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,46; 37,04</t>
+          <t>14,57; 38,96</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>127,67%</t>
+          <t>133,1%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>104,26%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,97; 249,01</t>
+          <t>3,93; 245,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,88; 297,8</t>
+          <t>14,56; 292,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,93; 312,42</t>
+          <t>33,75; 320,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 122,45</t>
+          <t>-22,0; 133,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,06; 102,0</t>
+          <t>-41,14; 96,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 151,67</t>
+          <t>-3,63; 143,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,28; 153,62</t>
+          <t>14,39; 153,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,26; 159,78</t>
+          <t>8,1; 162,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,33; 187,56</t>
+          <t>42,87; 213,91</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,38</t>
+          <t>14,4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,49</t>
+          <t>18,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14,56</t>
+          <t>16,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 20,85</t>
+          <t>-6,44; 20,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 13,28</t>
+          <t>-14,13; 14,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 23,63</t>
+          <t>0,23; 26,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 29,59</t>
+          <t>-7,91; 29,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 25,38</t>
+          <t>-11,99; 25,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 33,17</t>
+          <t>1,02; 33,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 19,15</t>
+          <t>-1,45; 19,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 13,81</t>
+          <t>-8,14; 14,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 24,84</t>
+          <t>7,75; 26,39</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>37,46%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 58,4</t>
+          <t>-13,65; 54,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 33,3</t>
+          <t>-28,95; 38,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 64,25</t>
+          <t>0,36; 68,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 82,93</t>
+          <t>-13,75; 87,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,73; 73,56</t>
+          <t>-21,25; 72,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 103,63</t>
+          <t>1,55; 98,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 48,37</t>
+          <t>-3,66; 50,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 33,92</t>
+          <t>-16,18; 37,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 64,69</t>
+          <t>16,21; 68,3</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23,29</t>
+          <t>16,85</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-18,66</t>
+          <t>4,04</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>15,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 25,73</t>
+          <t>-6,09; 24,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 3,67</t>
+          <t>-22,78; 3,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,99; 40,25</t>
+          <t>-0,25; 33,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 9,36</t>
+          <t>-31,53; 8,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 17,85</t>
+          <t>-19,01; 18,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,97; 11,85</t>
+          <t>-12,5; 23,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 16,72</t>
+          <t>-9,51; 16,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 6,54</t>
+          <t>-16,93; 6,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-24,2; 23,29</t>
+          <t>2,97; 26,83</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-28,34%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 71,22</t>
+          <t>-12,43; 70,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-46,94; 9,26</t>
+          <t>-45,52; 9,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,52; 114,77</t>
+          <t>0,62; 94,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,85; 15,75</t>
+          <t>-43,07; 17,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,89; 33,3</t>
+          <t>-25,14; 34,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,29; 19,45</t>
+          <t>-15,89; 46,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 37,44</t>
+          <t>-17,32; 36,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 14,66</t>
+          <t>-30,2; 14,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-45,3; 49,53</t>
+          <t>5,59; 62,44</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23,02</t>
+          <t>21,01</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,18</t>
+          <t>21,66</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20,31</t>
+          <t>20,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-23,39; 4,8</t>
+          <t>-23,31; 4,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 13,06</t>
+          <t>-13,2; 13,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,74; 33,33</t>
+          <t>9,39; 32,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 27,95</t>
+          <t>-4,08; 27,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 33,44</t>
+          <t>-0,86; 32,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 32,16</t>
+          <t>8,91; 34,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 10,39</t>
+          <t>-11,77; 9,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 17,92</t>
+          <t>-3,12; 16,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,39; 29,12</t>
+          <t>11,65; 28,2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,47; 9,28</t>
+          <t>-36,47; 8,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 24,61</t>
+          <t>-21,52; 27,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,35; 66,05</t>
+          <t>15,02; 63,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 63,44</t>
+          <t>-6,92; 63,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 79,77</t>
+          <t>0,44; 75,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,41; 76,65</t>
+          <t>15,01; 83,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 21,45</t>
+          <t>-19,26; 18,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 35,49</t>
+          <t>-5,04; 33,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,55; 57,75</t>
+          <t>19,28; 56,2</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18,43</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,16</t>
+          <t>16,05</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15,22</t>
+          <t>18,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 10,52</t>
+          <t>-3,76; 10,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 6,68</t>
+          <t>-7,6; 7,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,14; 25,33</t>
+          <t>10,54; 24,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 16,13</t>
+          <t>-4,02; 15,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 19,33</t>
+          <t>-0,47; 18,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 18,62</t>
+          <t>7,91; 23,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 11,08</t>
+          <t>-0,27; 10,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 9,97</t>
+          <t>-2,02; 10,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,18; 21,17</t>
+          <t>13,33; 23,63</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>40,07%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 25,52</t>
+          <t>-8,31; 25,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 16,45</t>
+          <t>-16,43; 17,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23,74; 63,93</t>
+          <t>21,72; 61,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 34,81</t>
+          <t>-7,05; 34,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 41,95</t>
+          <t>-0,81; 40,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 38,56</t>
+          <t>13,97; 51,77</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 25,82</t>
+          <t>-0,8; 25,35</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 22,95</t>
+          <t>-4,13; 23,7</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11,51; 48,91</t>
+          <t>26,93; 54,31</t>
         </is>
       </c>
     </row>
